--- a/AVGO.xlsx
+++ b/AVGO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F6C593-E98D-4E5A-9EE0-95BED5F1D5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D6E6A8-77DF-46F3-9494-52870FA7A05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-210" yWindow="4790" windowWidth="23600" windowHeight="13830" xr2:uid="{70329CC5-8756-4BA4-A5C1-E709DAADAB52}"/>
+    <workbookView xWindow="500" yWindow="1650" windowWidth="20990" windowHeight="18600" activeTab="1" xr2:uid="{70329CC5-8756-4BA4-A5C1-E709DAADAB52}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -367,7 +367,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -394,12 +394,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -481,14 +475,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>32524</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>20617</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>32524</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>20617</xdr:colOff>
       <xdr:row>70</xdr:row>
       <xdr:rowOff>125452</xdr:rowOff>
     </xdr:to>
@@ -505,8 +499,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9763899" y="0"/>
-          <a:ext cx="0" cy="11103015"/>
+          <a:off x="10331430" y="0"/>
+          <a:ext cx="0" cy="11261765"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1226,8 +1220,7 @@
         <v>46056</v>
       </c>
       <c r="Q3" s="14">
-        <f>+M3+365</f>
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="R3" s="14">
         <f>+N3+365</f>
@@ -1298,14 +1291,22 @@
         <v>82</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
+      <c r="D6" s="8">
+        <v>7107</v>
+      </c>
+      <c r="E6" s="8">
+        <v>6808</v>
+      </c>
       <c r="F6" s="8">
         <v>6941</v>
       </c>
       <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+      <c r="H6" s="8">
+        <v>7390</v>
+      </c>
+      <c r="I6" s="8">
+        <v>7202</v>
+      </c>
       <c r="J6" s="8">
         <v>7274</v>
       </c>
@@ -1316,13 +1317,20 @@
       <c r="L6" s="8">
         <v>8212</v>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
+      <c r="M6" s="8">
+        <v>8408</v>
+      </c>
+      <c r="N6" s="8">
+        <v>9166</v>
+      </c>
       <c r="O6" s="8">
         <v>11072</v>
       </c>
       <c r="P6" s="8">
         <v>12515</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>15009</v>
       </c>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
@@ -1332,14 +1340,22 @@
         <v>83</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="D7" s="8">
+        <v>1808</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1925</v>
+      </c>
       <c r="F7" s="8">
         <v>1935</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
+      <c r="H7" s="8">
+        <v>4571</v>
+      </c>
+      <c r="I7" s="8">
+        <v>5285</v>
+      </c>
       <c r="J7" s="8">
         <v>5798</v>
       </c>
@@ -1350,13 +1366,20 @@
       <c r="L7" s="8">
         <v>6704</v>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
+      <c r="M7" s="8">
+        <v>6596</v>
+      </c>
+      <c r="N7" s="8">
+        <v>6786</v>
+      </c>
       <c r="O7" s="8">
         <v>6943</v>
       </c>
       <c r="P7" s="8">
         <v>6796</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>7178</v>
       </c>
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
@@ -1445,21 +1468,26 @@
         <v>8930</v>
       </c>
       <c r="D10" s="10">
+        <f>+D7+D6</f>
         <v>8915</v>
       </c>
       <c r="E10" s="10">
+        <f>+E7+E6</f>
         <v>8733</v>
       </c>
       <c r="F10" s="10">
+        <f>+F7+F6</f>
         <v>8876</v>
       </c>
       <c r="G10" s="10">
         <v>9295</v>
       </c>
       <c r="H10" s="10">
+        <f>+H7+H6</f>
         <v>11961</v>
       </c>
       <c r="I10" s="10">
+        <f>+I7+I6</f>
         <v>12487</v>
       </c>
       <c r="J10" s="10">
@@ -1486,7 +1514,7 @@
         <v>19311</v>
       </c>
       <c r="Q10" s="10">
-        <v>22000</v>
+        <v>22187</v>
       </c>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
@@ -1559,6 +1587,9 @@
         <f>4041+638</f>
         <v>4679</v>
       </c>
+      <c r="Q11" s="8">
+        <v>5301</v>
+      </c>
       <c r="X11" s="8">
         <v>6555</v>
       </c>
@@ -1634,7 +1665,10 @@
         <f>+P10-P11</f>
         <v>14632</v>
       </c>
-      <c r="Q12" s="8"/>
+      <c r="Q12" s="8">
+        <f>+Q10-Q11</f>
+        <v>16886</v>
+      </c>
       <c r="R12" s="8"/>
       <c r="S12" s="8"/>
       <c r="T12" s="8"/>
@@ -1705,6 +1739,9 @@
       <c r="P13" s="8">
         <v>2965</v>
       </c>
+      <c r="Q13" s="8">
+        <v>2995</v>
+      </c>
       <c r="X13" s="8">
         <v>4854</v>
       </c>
@@ -1766,6 +1803,9 @@
       <c r="P14" s="8">
         <v>1019</v>
       </c>
+      <c r="Q14" s="8">
+        <v>1055</v>
+      </c>
       <c r="X14" s="8">
         <v>1347</v>
       </c>
@@ -1830,7 +1870,7 @@
         <v>3776</v>
       </c>
       <c r="N15" s="8">
-        <f t="shared" ref="N15:P15" si="4">+N13+N14</f>
+        <f t="shared" ref="N15:Q15" si="4">+N13+N14</f>
         <v>4122</v>
       </c>
       <c r="O15" s="8">
@@ -1841,6 +1881,10 @@
         <f t="shared" si="4"/>
         <v>3984</v>
       </c>
+      <c r="Q15" s="8">
+        <f t="shared" si="4"/>
+        <v>4050</v>
+      </c>
       <c r="X15" s="8">
         <f t="shared" ref="X15:Y15" si="5">+X14+X13</f>
         <v>6201</v>
@@ -1907,7 +1951,7 @@
         <v>7932</v>
       </c>
       <c r="N16" s="8">
-        <f t="shared" ref="N16:P16" si="8">+N12-N15</f>
+        <f t="shared" ref="N16:Q16" si="8">+N12-N15</f>
         <v>8126</v>
       </c>
       <c r="O16" s="8">
@@ -1918,6 +1962,10 @@
         <f t="shared" si="8"/>
         <v>10648</v>
       </c>
+      <c r="Q16" s="8">
+        <f t="shared" si="8"/>
+        <v>12836</v>
+      </c>
       <c r="X16" s="8">
         <f t="shared" ref="X16:Y16" si="9">+X12-X15</f>
         <v>14694</v>
@@ -1994,6 +2042,9 @@
       <c r="P17" s="8">
         <v>-801</v>
       </c>
+      <c r="Q17" s="8">
+        <v>-776</v>
+      </c>
       <c r="X17" s="8">
         <f>-1885+131</f>
         <v>-1754</v>
@@ -2060,7 +2111,7 @@
         <v>7188</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" ref="N18:P18" si="12">+N16+N17</f>
+        <f t="shared" ref="N18:Q18" si="12">+N16+N17</f>
         <v>7524</v>
       </c>
       <c r="O18" s="8">
@@ -2071,6 +2122,10 @@
         <f t="shared" si="12"/>
         <v>9847</v>
       </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="12"/>
+        <v>12060</v>
+      </c>
       <c r="X18" s="8">
         <f>+X16+X17</f>
         <v>12940</v>
@@ -2137,7 +2192,9 @@
       <c r="P19" s="8">
         <v>846</v>
       </c>
-      <c r="Q19" s="8"/>
+      <c r="Q19" s="8">
+        <v>820</v>
+      </c>
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
       <c r="T19" s="8"/>
@@ -2211,7 +2268,7 @@
         <v>7068</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" ref="N20:P20" si="15">+N18-N19</f>
+        <f t="shared" ref="N20:Q20" si="15">+N18-N19</f>
         <v>6379</v>
       </c>
       <c r="O20" s="8">
@@ -2222,6 +2279,10 @@
         <f t="shared" si="15"/>
         <v>9001</v>
       </c>
+      <c r="Q20" s="8">
+        <f t="shared" si="15"/>
+        <v>11240</v>
+      </c>
       <c r="X20" s="10">
         <f>+X18-X19</f>
         <v>12612</v>
@@ -2288,7 +2349,7 @@
         <v>1.4645669291338583</v>
       </c>
       <c r="N21" s="11">
-        <f t="shared" ref="N21:P21" si="18">+N20/N22</f>
+        <f t="shared" ref="N21:Q21" si="18">+N20/N22</f>
         <v>1.312551440329218</v>
       </c>
       <c r="O21" s="11">
@@ -2299,6 +2360,10 @@
         <f t="shared" si="18"/>
         <v>1.8414484451718494</v>
       </c>
+      <c r="Q21" s="8">
+        <f t="shared" si="18"/>
+        <v>2.3051681706316653</v>
+      </c>
       <c r="X21" s="11">
         <f>+X20/X22</f>
         <v>2.9398601398601398</v>
@@ -2363,6 +2428,9 @@
       <c r="P22" s="8">
         <v>4888</v>
       </c>
+      <c r="Q22" s="8">
+        <v>4876</v>
+      </c>
       <c r="X22" s="8">
         <v>4290</v>
       </c>
@@ -2424,7 +2492,7 @@
       </c>
       <c r="Q26" s="9">
         <f t="shared" si="21"/>
-        <v>0.46627565982404695</v>
+        <v>0.47873900293255134</v>
       </c>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
@@ -2504,6 +2572,10 @@
         <f t="shared" si="23"/>
         <v>0.75770286365284034</v>
       </c>
+      <c r="Q27" s="9">
+        <f t="shared" ref="Q27" si="24">+Q12/Q10</f>
+        <v>0.7610763059449227</v>
+      </c>
       <c r="X27" s="9">
         <f>+X12/X10</f>
         <v>0.76120218579234977</v>
@@ -2526,23 +2598,23 @@
         <v>21</v>
       </c>
       <c r="C28" s="9">
-        <f t="shared" ref="C28:G28" si="24">+C16/C10</f>
+        <f t="shared" ref="C28:G28" si="25">+C16/C10</f>
         <v>0.56718924972004481</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.56062815479528882</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.55032634833390592</v>
       </c>
       <c r="F28" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.54731861198738174</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.54222700376546529</v>
       </c>
       <c r="H28" s="9">
@@ -2566,20 +2638,24 @@
         <v>0.56590238669884685</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" ref="M28:P28" si="25">+M16/M10</f>
+        <f t="shared" ref="M28:P28" si="26">+M16/M10</f>
         <v>0.52865902426019729</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.50940320962888663</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.53921731890091595</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.55139557765004399</v>
+      </c>
+      <c r="Q28" s="9">
+        <f t="shared" ref="Q28" si="27">+Q16/Q10</f>
+        <v>0.57853698111506735</v>
       </c>
       <c r="X28" s="9">
         <f>+X16/X10</f>
@@ -2955,39 +3031,39 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
       <c r="H39" s="8">
-        <f t="shared" ref="H39:P39" si="26">SUM(H32:H38)</f>
+        <f t="shared" ref="H39:P39" si="28">SUM(H32:H38)</f>
         <v>177870</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>175211</v>
       </c>
       <c r="J39" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>167966</v>
       </c>
       <c r="K39" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L39" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>165358</v>
       </c>
       <c r="M39" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N39" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>165621</v>
       </c>
       <c r="O39" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>171092</v>
       </c>
       <c r="P39" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>169903</v>
       </c>
       <c r="Q39" s="8"/>
@@ -3338,19 +3414,19 @@
         <v>165358</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" ref="M47:P47" si="27">SUM(M41:M46)</f>
+        <f t="shared" ref="M47:P47" si="29">SUM(M41:M46)</f>
         <v>0</v>
       </c>
       <c r="N47" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>165621</v>
       </c>
       <c r="O47" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>171092</v>
       </c>
       <c r="P47" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>169903</v>
       </c>
       <c r="Q47" s="8"/>
@@ -3371,39 +3447,39 @@
         <v>39</v>
       </c>
       <c r="H49" s="8">
-        <f t="shared" ref="H49:P49" si="28">+H20</f>
+        <f t="shared" ref="H49:P49" si="30">+H20</f>
         <v>3423</v>
       </c>
       <c r="I49" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>4809</v>
       </c>
       <c r="J49" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1266</v>
       </c>
       <c r="K49" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>5483</v>
       </c>
       <c r="L49" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>6397</v>
       </c>
       <c r="M49" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7068</v>
       </c>
       <c r="N49" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>6379</v>
       </c>
       <c r="O49" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>9075</v>
       </c>
       <c r="P49" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>9001</v>
       </c>
     </row>
@@ -3601,31 +3677,31 @@
         <v>44</v>
       </c>
       <c r="H58" s="10">
-        <f t="shared" ref="H58:N58" si="29">SUM(H50:H57)</f>
+        <f t="shared" ref="H58:N58" si="31">SUM(H50:H57)</f>
         <v>4815</v>
       </c>
       <c r="I58" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>4580</v>
       </c>
       <c r="J58" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>4963</v>
       </c>
       <c r="K58" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L58" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M58" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>6555</v>
       </c>
       <c r="N58" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7166</v>
       </c>
       <c r="X58" s="10">
